--- a/data/demo/Pulsarq-Sales-2026-07-20~2026-07-20.xlsx
+++ b/data/demo/Pulsarq-Sales-2026-07-20~2026-07-20.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>2026-07-20</t>
   </si>
@@ -23,43 +23,64 @@
     <t>Altavoces Inalámbricos，Mini Karaoke Portátil para Niños | Sonido Nítido Alta Fidelidad, Bocina Bluetooth 5.3 con Micrófono Inalámbrico, Diversión Musical Familiar para Fiestas y Reuniones en Casa</t>
   </si>
   <si>
-    <t>MX$1,074.00</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>MX$2,482.00</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>1.84</t>
+  </si>
+  <si>
+    <t>MX$99.28</t>
+  </si>
+  <si>
+    <t>604723306417839</t>
+  </si>
+  <si>
+    <t>Altavoz inalámbrico portátil con Luces RGB, Radio FM y Manija - 5h Duración, TWS, TF Card, Compacto y Recargable via USB，Perfecto para viajes, fiestas y gaming</t>
+  </si>
+  <si>
+    <t>MX$683.49</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>2.29</t>
+  </si>
+  <si>
+    <t>MX$97.64</t>
+  </si>
+  <si>
+    <t>604721964231697</t>
+  </si>
+  <si>
+    <t>Bocina Radio FM/Reproductor, Compatible con Tarjeta TF, USB, Bluetooth, Aplicable para celular, computadora, Ipad y consola</t>
+  </si>
+  <si>
+    <t>MX$157.50</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>1.00</t>
   </si>
   <si>
-    <t>MX$53.70</t>
-  </si>
-  <si>
-    <t>604723306417839</t>
-  </si>
-  <si>
-    <t>Altavoz inalámbrico portátil con Luces RGB, Radio FM y Manija - 5h Duración, TWS, TF Card, Compacto y Recargable via USB，Perfecto para viajes, fiestas y gaming</t>
-  </si>
-  <si>
-    <t>MX$632.49</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>2.50</t>
-  </si>
-  <si>
-    <t>MX$105.41</t>
+    <t>MX$78.75</t>
   </si>
   <si>
     <t>604901279130455</t>
@@ -72,15 +93,6 @@
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>604721964231697</t>
-  </si>
-  <si>
-    <t>Bocina Radio FM/Reproductor, Compatible con Tarjeta TF, USB, Bluetooth, Aplicable para celular, computadora, Ipad y consola</t>
-  </si>
-  <si>
-    <t>MX$80.00</t>
   </si>
 </sst>
 </file>
@@ -230,13 +242,13 @@
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -244,28 +256,28 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -273,28 +285,28 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H4" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -302,28 +314,28 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
         <v>21</v>
       </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s">
-        <v>6</v>
-      </c>
       <c r="I5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
